--- a/query_devops.xlsx
+++ b/query_devops.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\archlinux\home\murilo\projetos\calendarizacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F53611-D0D7-4144-84A1-073CAC7D272C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99DA44B-7A95-454A-BF67-688B0DFA92D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{A1B5FDA2-366A-448C-8A50-F88973F13F5A}"/>
   </bookViews>
@@ -11277,7 +11277,7 @@
       <c r="K133" s="7"/>
     </row>
   </sheetData>
-  <dataValidations count="19">
+  <dataValidations count="120">
     <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A2" xr:uid="{44C34D34-037E-4EC0-9C63-9425233FE9FE}">
       <formula1>"ID"</formula1>
     </dataValidation>
@@ -11337,6 +11337,333 @@
     <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="K8" xr:uid="{FDC821A5-0425-4BB0-9FCE-B2884DDFCEE7}">
       <formula1>" "</formula1>
     </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A3" xr:uid="{69DEFA28-A653-4152-B66C-0F9AB672BA88}">
+      <formula1>"2417031"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B3" xr:uid="{40E797B4-A088-49ED-A1AD-EB3D897DFDE5}">
+      <formula1>"Épico"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C3" xr:uid="{2D76A67D-092F-4D8A-9939-B4265655576A}">
+      <formula1>"30/04/2026 17:46"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="E3" xr:uid="{E1449B26-94E9-42A1-9DCF-2F0AE8BD0911}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F3" xr:uid="{0A7329A7-F0EA-43CF-B339-77EFA9BF6A72}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G3" xr:uid="{A3A483BB-4D67-4B9F-9A08-C7C1B05B5B19}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H3" xr:uid="{AC1CBB66-D979-421A-8194-9F91E23BBC39}">
+      <formula1>VSTS_ValidationRange_d7f8f88d605c465dbba378dda23b2aaa</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I3" xr:uid="{2C95EF0E-0434-4264-9C5E-7DA495B0EB71}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A133" xr:uid="{01E6D485-83C3-466E-BA56-54D05C052596}">
+      <formula1>"2508409"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B133" xr:uid="{5C79F785-8DE2-49E0-B055-E434D55253DD}">
+      <formula1>"Business Story"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C133" xr:uid="{89B3F53B-AD2E-442E-856F-A3D11077463B}">
+      <formula1>"15/05/2026 12:26"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F133" xr:uid="{8A077CFB-09AB-45A3-AF62-DF1EB9BB6E8E}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G133" xr:uid="{B0354654-B28F-4E70-B066-638907CE36B9}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H133" xr:uid="{6A519BDF-2873-469E-917C-546FB01A1064}">
+      <formula1>VSTS_ValidationRange_10fbcead235943acab81475ae65b7bcd</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I133" xr:uid="{1CAD05BA-4E49-4B7C-969F-814EBD654520}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="K133" xr:uid="{1BFAFE5F-83AD-468F-BF3B-19203BB06CBC}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A130" xr:uid="{C10FC9EF-FCFC-41D6-B8AE-EB884636529F}">
+      <formula1>"2508410"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B130" xr:uid="{4FB45557-119C-46FB-8641-4B2DF887CBED}">
+      <formula1>"Demanda"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C130" xr:uid="{7F5C83DB-44F0-4A2D-8CBD-B3E65BEB7B7D}">
+      <formula1>"11/05/2026 17:39"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="E130" xr:uid="{90E8AC90-A480-4A30-9F26-58800ECAF446}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F130" xr:uid="{6446F079-D485-4363-9539-1FCC0694BF26}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G130" xr:uid="{55C82FB6-F532-4189-9AA5-E09E7B69200E}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H130" xr:uid="{2D3AF083-6C93-4CF7-B1EA-015F1539CAB3}">
+      <formula1>VSTS_ValidationRange_d7f8f88d605c465dbba378dda23b2aaa</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I130" xr:uid="{1B2C02EB-436E-4C00-B4FD-CA6604244926}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="J130" xr:uid="{9A4C4032-3913-4C63-9F17-BF7364ED6B79}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="K130" xr:uid="{FE86A7E3-1995-4A30-AC19-DA5B5917BFFA}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A124" xr:uid="{A47C2BE6-5CF7-4C37-AC96-05215ACEF686}">
+      <formula1>"2471673"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B124" xr:uid="{938D67CD-A9A6-4574-A81D-DD7F98968E03}">
+      <formula1>"Demanda"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C124" xr:uid="{CA356BEB-BFAB-4A49-B2C5-5681C1C3A84D}">
+      <formula1>"24/04/2026 09:32"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="E124" xr:uid="{4099334B-FFF4-4A93-8C13-41956DA046E0}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F124" xr:uid="{D3092857-C766-426D-9364-739C5A881EE8}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G124" xr:uid="{2DA52607-A28D-4B56-A950-9BE9B9FB7FE9}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H124" xr:uid="{2ACF7281-F6F8-475F-AA7D-1279517738D7}">
+      <formula1>VSTS_ValidationRange_d7f8f88d605c465dbba378dda23b2aaa</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I124" xr:uid="{9EA82D7C-1F2A-41C4-9B84-F7C09F02823D}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="J124" xr:uid="{8139F6AD-299D-427A-A7DC-E90898EAD562}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="K124" xr:uid="{DA84448B-6A4B-4133-B14F-162C8843D353}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A122" xr:uid="{FB52757F-D582-4DA6-AAAA-E8EE21CD5CE4}">
+      <formula1>"2466111"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B122" xr:uid="{60DC6FC0-034E-4F8D-94F3-989045890C21}">
+      <formula1>"Demanda"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C122" xr:uid="{E15EB447-FF64-4869-81D6-BEE47FF7A82B}">
+      <formula1>"22/04/2026 16:24"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="E122" xr:uid="{1E2AD33E-AB48-464C-9DBA-F4B9910130C1}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F122" xr:uid="{A5D9B03D-1FE4-4F9C-A0B3-B7D00AEB89B1}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G122" xr:uid="{A8832C99-7D49-4987-9D2D-FBF815687D3C}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H122" xr:uid="{B41988EF-005D-4BDB-8FBA-0B8C80606D2F}">
+      <formula1>VSTS_ValidationRange_d7f8f88d605c465dbba378dda23b2aaa</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I122" xr:uid="{F9ECFF75-A877-46E8-B995-066357611101}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="J122" xr:uid="{4CE5DE2D-F5A6-4198-8B1F-5DFD1878D401}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="K122" xr:uid="{6481B904-F010-484F-9003-9CCBDB756F04}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A123" xr:uid="{59B7B427-ADED-476C-A1CB-E4D67CB7788B}">
+      <formula1>"2462436"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B123" xr:uid="{D18B742E-63C7-4D8F-9B4E-B5E75506535B}">
+      <formula1>"Business Story"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C123" xr:uid="{94428160-11E9-47AF-8674-F6383F08F1E1}">
+      <formula1>"27/04/2026 15:48"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F123" xr:uid="{E4051953-7D56-4752-9FB0-BA85E1D95251}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G123" xr:uid="{FA0DCAE9-98B2-4196-B629-EC8D2C8B206E}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H123" xr:uid="{390A0308-5F98-4FE7-99CC-D91BD377A725}">
+      <formula1>VSTS_ValidationRange_10fbcead235943acab81475ae65b7bcd</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I123" xr:uid="{073C1A5A-CAA4-46C0-9780-587083632420}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="K123" xr:uid="{56946795-36F6-4F42-8311-4C1F43155A63}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A127" xr:uid="{8903E970-3DE9-4B90-911D-C2AECA8F1E0B}">
+      <formula1>"2471753"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B127" xr:uid="{A8FD4B81-1F64-491B-AD71-B2CDA3B334F6}">
+      <formula1>"Demanda"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C127" xr:uid="{50DB47AE-9528-4E43-9D68-9D1F1D4FAC0D}">
+      <formula1>"11/05/2026 15:39"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="E127" xr:uid="{22D64E64-DDD2-4F0C-8630-899281CBFFB5}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F127" xr:uid="{4091D302-770D-434F-968F-1DFBFC1F4BAC}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G127" xr:uid="{CDB01429-48FE-4925-AD95-7497884997ED}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H127" xr:uid="{F0E01B58-315E-43C7-8CCE-4A5C59D8D727}">
+      <formula1>VSTS_ValidationRange_d7f8f88d605c465dbba378dda23b2aaa</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I127" xr:uid="{CDF30A18-1631-4745-A72F-D5F74DAC395D}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="J127" xr:uid="{EAE4729E-B8DD-437A-9D03-BB7E6DA82CD3}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="K127" xr:uid="{841D9D10-050E-4492-A507-32A7651B8F92}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A126" xr:uid="{F77E423F-0795-4202-8B36-B9F7FD565104}">
+      <formula1>"2476881"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B126" xr:uid="{BDF52EED-2E17-4390-9EFC-5F4673EA2A0A}">
+      <formula1>"Analysis Activity"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C126" xr:uid="{245A5404-29B9-4FAD-8C44-7C0770D2D5A5}">
+      <formula1>"05/05/2026 09:23"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F126" xr:uid="{A6D1055C-44BC-4629-B98E-D9D11B7F26C6}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G126" xr:uid="{30FDD362-915E-40A7-8493-91135A0B2ABA}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H126" xr:uid="{AA1355C5-7D44-44FB-A014-CD93ECA06039}">
+      <formula1>VSTS_ValidationRange_10fbcead235943acab81475ae65b7bcd</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I126" xr:uid="{54ADAA00-BEB1-4278-AB13-4D128287D4D8}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="K126" xr:uid="{F376ADD1-5118-4928-9A4F-A538C920ABEA}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A125" xr:uid="{5135F80B-1FBF-4FE8-BF16-2A25DF94DF0D}">
+      <formula1>"2474386"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B125" xr:uid="{72A84FA6-470A-44EE-85E3-09C10737D9AD}">
+      <formula1>"Analysis Activity"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C125" xr:uid="{D91688F5-22F1-485E-897F-E662238B43C4}">
+      <formula1>"05/05/2026 09:24"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F125" xr:uid="{AF6E04B6-D1FE-4238-AB6A-B58344D488E9}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G125" xr:uid="{96C61FD4-66FD-4328-8C8A-7F339E0CD122}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H125" xr:uid="{58DBC203-6A6F-4F60-8E82-CD7449F76AC3}">
+      <formula1>VSTS_ValidationRange_10fbcead235943acab81475ae65b7bcd</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I125" xr:uid="{D87F5912-8933-4060-A98B-95C4D74248DC}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84027: This field is not available for this type of work item and must be left blank." prompt="Read-only" sqref="K125" xr:uid="{74F28698-9280-4A3E-B2B6-008861332DD6}">
+      <formula1>" "</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A121" xr:uid="{F667DD8E-3B84-4591-8D4D-6D5A4616D4E8}">
+      <formula1>"2492141"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B121" xr:uid="{D18EF2B2-B08E-4F90-A700-77411FA817A1}">
+      <formula1>"Technical Story"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C121" xr:uid="{68A194EA-4FF8-449E-9512-D445BCC98E07}">
+      <formula1>"11/05/2026 18:01"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F121" xr:uid="{EEC3D695-56C7-4C6A-8F8B-B1B29281CDE6}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G121" xr:uid="{657B27E9-F4E5-4CC0-B3FB-5F08553F5D28}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H121" xr:uid="{513C2A5E-99C1-4A13-BA9B-0F7DA8A9E045}">
+      <formula1>VSTS_ValidationRange_10fbcead235943acab81475ae65b7bcd</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I121" xr:uid="{4AA6B8B8-D098-425F-A970-C6FF66A7F77E}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A119" xr:uid="{45F321A2-DC4E-4513-B65C-4075F70F9DBC}">
+      <formula1>"2418329"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B119" xr:uid="{C54EB3DC-672C-4639-ABFA-A5A63053CB20}">
+      <formula1>"Technical Story"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C119" xr:uid="{5A97898E-6FF5-4083-BF6A-9A60D7509898}">
+      <formula1>"06/05/2026 10:11"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F119" xr:uid="{D97DDE52-DF9E-4DD4-A119-0955F1725453}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G119" xr:uid="{63B05F6B-8198-4B1C-AD98-6461D46148FE}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H119" xr:uid="{C0EF6A52-3A3E-46FB-95D1-481A849153A6}">
+      <formula1>VSTS_ValidationRange_10fbcead235943acab81475ae65b7bcd</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I119" xr:uid="{64D8A211-6D16-4A59-8930-AED4DEC32743}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="A131" xr:uid="{8165D869-2B50-4563-A2AD-5CD7FB6EF88C}">
+      <formula1>"2508413"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="B131" xr:uid="{C3FA07CC-7138-4D32-90AA-0BFAE1359B00}">
+      <formula1>"Technical Story"</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Read-only column" error="TF84013: You cannot modify a field that is read-only or a work item that restricts updates to valid users based on current permissions." prompt="Read-only" sqref="C131" xr:uid="{CFCFA892-B5D1-4233-8B8C-421CA9D4E25A}">
+      <formula1>"14/05/2026 20:22"</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" sqref="F131" xr:uid="{A236E0F3-E8FC-436F-81E9-63412BE4C6D8}">
+      <formula1>1</formula1>
+      <formula2>255</formula2>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" sqref="G131" xr:uid="{6867B70B-1AED-4A60-88A8-EE96532DE326}">
+      <formula1>VSTS_ValidationRange_d53b364a297d45608334d5f4f5d1997f</formula1>
+    </dataValidation>
+    <dataValidation type="list" operator="equal" showInputMessage="1" showErrorMessage="1" errorTitle="Microsoft Excel" error="TF84042: The value you entered is not supported in this field. Select a supported value from the list." sqref="H131" xr:uid="{76DC53BD-9F36-49E6-B146-6FDE8BEF67C7}">
+      <formula1>VSTS_ValidationRange_10fbcead235943acab81475ae65b7bcd</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" sqref="I131" xr:uid="{CA98B0F6-603E-459B-A4C7-CF9E0F94DEC5}">
+      <formula1>0</formula1>
+      <formula2>32767</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -11361,7 +11688,7 @@
         <v>11</v>
       </c>
       <c r="C1" s="3">
-        <v>46142.730300925927</v>
+        <v>46156.848761574074</v>
       </c>
       <c r="D1" s="4">
         <v>0.25</v>
